--- a/selenium-tests/StainScope_Master_All_Tests_Report.xlsx
+++ b/selenium-tests/StainScope_Master_All_Tests_Report.xlsx
@@ -16,7 +16,7 @@
     <t>🏆 StainScope Platform - Master Quality &amp; Security Certification</t>
   </si>
   <si>
-    <t>Generated: Fri, 21 Aug 2026 09:23:01 GMT | CI/CD Execution Status: 100% GREEN (PASSED) | Master Certification Grade: A+</t>
+    <t>Generated: Fri, 21 Aug 2026 09:28:01 GMT | CI/CD Execution Status: 100% GREEN (PASSED) | Master Certification Grade: A+</t>
   </si>
   <si>
     <t xml:space="preserve">TOTAL TEST CASES
